--- a/kaizen-sitemap.xlsx
+++ b/kaizen-sitemap.xlsx
@@ -490,7 +490,7 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="32" customWidth="1" min="6" max="6"/>
     <col width="55" customWidth="1" min="7" max="7"/>
   </cols>
@@ -505,7 +505,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Static multipage site · HTML / CSS / JS · 4 pages</t>
+          <t>https://kaizenconcretos.com · Static multipage site · HTML / CSS / JS · 4 pages</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>URL path</t>
+          <t>URL</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>https://kaizenconcretos.com/</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>/nosotros.html</t>
+          <t>https://kaizenconcretos.com/nosotros.html</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>/productos.html</t>
+          <t>https://kaizenconcretos.com/productos.html</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>/contacto.html</t>
+          <t>https://kaizenconcretos.com/contacto.html</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
